--- a/reports/banrep.xlsx
+++ b/reports/banrep.xlsx
@@ -1,153 +1,191 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30224"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A5B12D0-46D9-48B4-850F-8DA938B5E3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Bots IA" sheetId="1" r:id="rId1"/>
+    <sheet name="Bots IA" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>Fecha</t>
-  </si>
-  <si>
-    <t>GPTBot</t>
-  </si>
-  <si>
-    <t>OAI-SearchBot</t>
-  </si>
-  <si>
-    <t>PerplexityBot</t>
-  </si>
-  <si>
-    <t>2026-06-03</t>
-  </si>
-  <si>
-    <t>2026-06-04</t>
-  </si>
-  <si>
-    <t>2026-06-05</t>
-  </si>
-  <si>
-    <t>2026-06-06</t>
-  </si>
-  <si>
-    <t>2026-06-07</t>
-  </si>
-  <si>
-    <t>2026-06-08</t>
-  </si>
-  <si>
-    <t>2026-06-09</t>
-  </si>
-  <si>
-    <t>2026-06-10</t>
-  </si>
-  <si>
-    <t>2026-06-11</t>
-  </si>
-  <si>
-    <t>2026-06-12</t>
-  </si>
-  <si>
-    <t>2026-06-13</t>
-  </si>
-  <si>
-    <t>2026-06-14</t>
-  </si>
-  <si>
-    <t>2026-06-15</t>
-  </si>
-  <si>
-    <t>2026-06-16</t>
-  </si>
-  <si>
-    <t>2026-06-17</t>
-  </si>
-  <si>
-    <t>2026-06-18</t>
-  </si>
-  <si>
-    <t>2026-06-19</t>
-  </si>
-  <si>
-    <t>2026-06-20</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>2026-06-22</t>
-  </si>
-  <si>
-    <t>2026-06-23</t>
-  </si>
-  <si>
-    <t>2026-06-24</t>
-  </si>
-  <si>
-    <t>2026-06-25</t>
-  </si>
-  <si>
-    <t>2026-06-26</t>
-  </si>
-  <si>
-    <t>2026-06-27</t>
-  </si>
-  <si>
-    <t>2026-06-28</t>
-  </si>
-  <si>
-    <t>2026-06-29</t>
-  </si>
-  <si>
-    <t>2026-06-30</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <si>
+    <t xml:space="preserve">Fecha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPTBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAI-SearchBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PerplexityBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,63 +197,80 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+  <cellXfs count="3">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -250,252 +305,152 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.16"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,413 +464,517 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="0" t="n">
         <v>488</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0" t="n">
         <v>4033</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="0" t="n">
         <v>1662</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="0" t="n">
         <v>770</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0" t="n">
         <v>5525</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="0" t="n">
         <v>1893</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
         <v>6</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="0" t="n">
         <v>770</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="0" t="n">
         <v>5525</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="0" t="n">
         <v>1893</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="0" t="n">
         <v>923</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="0" t="n">
         <v>6233</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="0" t="n">
         <v>2083</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="0" t="n">
         <v>56</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="0" t="n">
         <v>729</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="0" t="n">
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="0" t="n">
         <v>102</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="0" t="n">
         <v>1855</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="0" t="n">
         <v>372</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="0" t="n">
         <v>1415</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="0" t="n">
         <v>3552</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="0" t="n">
         <v>660</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="0" t="n">
         <v>19890</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="0" t="n">
         <v>4615</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="0" t="n">
         <v>1323</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="0" t="n">
         <v>26704</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="0" t="n">
         <v>5671</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="0" t="n">
         <v>1576</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="0" t="n">
         <v>29937</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="0" t="n">
         <v>7463</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="0" t="n">
         <v>1843</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="0" t="n">
         <v>31036</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="0" t="n">
         <v>8124</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="0" t="n">
         <v>2158</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="0" t="n">
         <v>1595</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="0" t="n">
         <v>601</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="0" t="n">
         <v>205</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="0" t="n">
         <v>9020</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="0" t="n">
         <v>1240</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="0" t="n">
         <v>472</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="0" t="n">
         <v>29765</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="0" t="n">
         <v>2924</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="0" t="n">
         <v>895</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="0" t="n">
         <v>33115</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="0" t="n">
         <v>4607</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="0" t="n">
         <v>1142</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="0" t="n">
         <v>36890</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="0" t="n">
         <v>5640</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="0" t="n">
         <v>1347</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="0" t="n">
         <v>39235</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="0" t="n">
         <v>6626</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="0" t="n">
         <v>1699</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="0" t="n">
         <v>43204</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="0" t="n">
         <v>7594</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="0" t="n">
         <v>1930</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="0" t="n">
         <v>3556</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="0" t="n">
         <v>787</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="0" t="n">
         <v>238</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="0" t="n">
         <v>8490</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="0" t="n">
         <v>2261</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="0" t="n">
         <v>527</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="s">
         <v>24</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="0" t="n">
         <v>21937</v>
       </c>
-      <c r="C22">
+      <c r="C22" s="0" t="n">
         <v>4297</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="0" t="n">
         <v>743</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="0" t="n">
         <v>28919</v>
       </c>
-      <c r="C23">
+      <c r="C23" s="0" t="n">
         <v>6563</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="0" t="n">
         <v>953</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="0" t="n">
         <v>38219</v>
       </c>
-      <c r="C24">
+      <c r="C24" s="0" t="n">
         <v>7716</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="0" t="n">
         <v>1250</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="0" t="n">
         <v>39241</v>
       </c>
-      <c r="C25">
+      <c r="C25" s="0" t="n">
         <v>8475</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="0" t="n">
         <v>1511</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
         <v>28</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="0" t="n">
         <v>39955</v>
       </c>
-      <c r="C26">
+      <c r="C26" s="0" t="n">
         <v>9973</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="0" t="n">
         <v>1711</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="0" t="n">
         <v>2225</v>
       </c>
-      <c r="C27">
+      <c r="C27" s="0" t="n">
         <v>1171</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="0" t="n">
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="0" t="n">
         <v>3896</v>
       </c>
-      <c r="C28">
+      <c r="C28" s="0" t="n">
         <v>2544</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="0" t="n">
         <v>1060</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="0" t="n">
         <v>6462</v>
       </c>
-      <c r="C29">
+      <c r="C29" s="0" t="n">
         <v>3907</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="0" t="n">
         <v>1281</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
         <v>32</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="0" t="n">
         <v>8079</v>
       </c>
-      <c r="C30">
+      <c r="C30" s="0" t="n">
         <v>5711</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="0" t="n">
         <v>1496</v>
       </c>
     </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="0" t="n">
+        <v>11459</v>
+      </c>
+      <c r="C31" s="0" t="n">
+        <v>7224</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" s="0" t="n">
+        <v>13392</v>
+      </c>
+      <c r="C32" s="0" t="n">
+        <v>8441</v>
+      </c>
+      <c r="D32" s="0" t="n">
+        <v>1838</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="0" t="n">
+        <v>14756</v>
+      </c>
+      <c r="C33" s="0" t="n">
+        <v>9375</v>
+      </c>
+      <c r="D33" s="0" t="n">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="0" t="n">
+        <v>1870</v>
+      </c>
+      <c r="C34" s="0" t="n">
+        <v>1312</v>
+      </c>
+      <c r="D34" s="0" t="n">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="0" t="n">
+        <v>3755</v>
+      </c>
+      <c r="C35" s="0" t="n">
+        <v>2663</v>
+      </c>
+      <c r="D35" s="0" t="n">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="0" t="n">
+        <v>6540</v>
+      </c>
+      <c r="C36" s="0" t="n">
+        <v>4051</v>
+      </c>
+      <c r="D36" s="0" t="n">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="0" t="n">
+        <v>9912</v>
+      </c>
+      <c r="C37" s="0" t="n">
+        <v>5590</v>
+      </c>
+      <c r="D37" s="0" t="n">
+        <v>1006</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/reports/banrep.xlsx
+++ b/reports/banrep.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Fecha</t>
   </si>
@@ -140,6 +140,27 @@
   </si>
   <si>
     <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
   </si>
 </sst>
 </file>
@@ -237,16 +258,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -442,532 +467,632 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>488</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>4033</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1662</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>770</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>5525</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>1893</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>770</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>5525</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>1893</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>923</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>6233</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>2083</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>729</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>161</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>102</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1855</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>372</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>1415</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>3552</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>660</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>19890</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>4615</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>1323</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>26704</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>5671</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>1576</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>29937</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="1" t="n">
         <v>7463</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="1" t="n">
         <v>1843</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>31036</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>8124</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="1" t="n">
         <v>2158</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>1595</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>601</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="1" t="n">
         <v>205</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>9020</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>1240</v>
       </c>
-      <c r="D14" s="0" t="n">
+      <c r="D14" s="1" t="n">
         <v>472</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>29765</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>2924</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="1" t="n">
         <v>895</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="0" t="n">
+      <c r="B16" s="1" t="n">
         <v>33115</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>4607</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="1" t="n">
         <v>1142</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="0" t="n">
+      <c r="B17" s="1" t="n">
         <v>36890</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>5640</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>1347</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="0" t="n">
+      <c r="B18" s="1" t="n">
         <v>39235</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>6626</v>
       </c>
-      <c r="D18" s="0" t="n">
+      <c r="D18" s="1" t="n">
         <v>1699</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="0" t="n">
+      <c r="B19" s="1" t="n">
         <v>43204</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>7594</v>
       </c>
-      <c r="D19" s="0" t="n">
+      <c r="D19" s="1" t="n">
         <v>1930</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="0" t="n">
+      <c r="B20" s="1" t="n">
         <v>3556</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="1" t="n">
         <v>787</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="1" t="n">
         <v>238</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="0" t="n">
+      <c r="B21" s="1" t="n">
         <v>8490</v>
       </c>
-      <c r="C21" s="0" t="n">
+      <c r="C21" s="1" t="n">
         <v>2261</v>
       </c>
-      <c r="D21" s="0" t="n">
+      <c r="D21" s="1" t="n">
         <v>527</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="0" t="n">
+      <c r="B22" s="1" t="n">
         <v>21937</v>
       </c>
-      <c r="C22" s="0" t="n">
+      <c r="C22" s="1" t="n">
         <v>4297</v>
       </c>
-      <c r="D22" s="0" t="n">
+      <c r="D22" s="1" t="n">
         <v>743</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="0" t="n">
+      <c r="B23" s="1" t="n">
         <v>28919</v>
       </c>
-      <c r="C23" s="0" t="n">
+      <c r="C23" s="1" t="n">
         <v>6563</v>
       </c>
-      <c r="D23" s="0" t="n">
+      <c r="D23" s="1" t="n">
         <v>953</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="0" t="n">
+      <c r="B24" s="1" t="n">
         <v>38219</v>
       </c>
-      <c r="C24" s="0" t="n">
+      <c r="C24" s="1" t="n">
         <v>7716</v>
       </c>
-      <c r="D24" s="0" t="n">
+      <c r="D24" s="1" t="n">
         <v>1250</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="0" t="n">
+      <c r="B25" s="1" t="n">
         <v>39241</v>
       </c>
-      <c r="C25" s="0" t="n">
+      <c r="C25" s="1" t="n">
         <v>8475</v>
       </c>
-      <c r="D25" s="0" t="n">
+      <c r="D25" s="1" t="n">
         <v>1511</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="0" t="n">
+      <c r="B26" s="1" t="n">
         <v>39955</v>
       </c>
-      <c r="C26" s="0" t="n">
+      <c r="C26" s="1" t="n">
         <v>9973</v>
       </c>
-      <c r="D26" s="0" t="n">
+      <c r="D26" s="1" t="n">
         <v>1711</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="0" t="n">
+      <c r="B27" s="1" t="n">
         <v>2225</v>
       </c>
-      <c r="C27" s="0" t="n">
+      <c r="C27" s="1" t="n">
         <v>1171</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="1" t="n">
         <v>185</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="0" t="n">
+      <c r="B28" s="1" t="n">
         <v>3896</v>
       </c>
-      <c r="C28" s="0" t="n">
+      <c r="C28" s="1" t="n">
         <v>2544</v>
       </c>
-      <c r="D28" s="0" t="n">
+      <c r="D28" s="1" t="n">
         <v>1060</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="0" t="n">
+      <c r="B29" s="1" t="n">
         <v>6462</v>
       </c>
-      <c r="C29" s="0" t="n">
+      <c r="C29" s="1" t="n">
         <v>3907</v>
       </c>
-      <c r="D29" s="0" t="n">
+      <c r="D29" s="1" t="n">
         <v>1281</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="0" t="n">
+      <c r="B30" s="1" t="n">
         <v>8079</v>
       </c>
-      <c r="C30" s="0" t="n">
+      <c r="C30" s="1" t="n">
         <v>5711</v>
       </c>
-      <c r="D30" s="0" t="n">
+      <c r="D30" s="1" t="n">
         <v>1496</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="0" t="n">
+      <c r="B31" s="1" t="n">
         <v>11459</v>
       </c>
-      <c r="C31" s="0" t="n">
+      <c r="C31" s="1" t="n">
         <v>7224</v>
       </c>
-      <c r="D31" s="2" t="n">
+      <c r="D31" s="3" t="n">
         <v>1661</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="0" t="n">
+      <c r="B32" s="1" t="n">
         <v>13392</v>
       </c>
-      <c r="C32" s="0" t="n">
+      <c r="C32" s="1" t="n">
         <v>8441</v>
       </c>
-      <c r="D32" s="0" t="n">
+      <c r="D32" s="1" t="n">
         <v>1838</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="0" t="n">
+      <c r="B33" s="1" t="n">
         <v>14756</v>
       </c>
-      <c r="C33" s="0" t="n">
+      <c r="C33" s="1" t="n">
         <v>9375</v>
       </c>
-      <c r="D33" s="0" t="n">
+      <c r="D33" s="1" t="n">
         <v>2134</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="0" t="n">
+      <c r="B34" s="1" t="n">
         <v>1870</v>
       </c>
-      <c r="C34" s="0" t="n">
+      <c r="C34" s="1" t="n">
         <v>1312</v>
       </c>
-      <c r="D34" s="0" t="n">
+      <c r="D34" s="1" t="n">
         <v>213</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="0" t="n">
+      <c r="B35" s="1" t="n">
         <v>3755</v>
       </c>
-      <c r="C35" s="0" t="n">
+      <c r="C35" s="1" t="n">
         <v>2663</v>
       </c>
-      <c r="D35" s="0" t="n">
+      <c r="D35" s="1" t="n">
         <v>433</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="0" t="n">
+      <c r="B36" s="1" t="n">
         <v>6540</v>
       </c>
-      <c r="C36" s="0" t="n">
+      <c r="C36" s="1" t="n">
         <v>4051</v>
       </c>
-      <c r="D36" s="0" t="n">
+      <c r="D36" s="1" t="n">
         <v>645</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="0" t="n">
+      <c r="B37" s="1" t="n">
         <v>9912</v>
       </c>
-      <c r="C37" s="0" t="n">
+      <c r="C37" s="1" t="n">
         <v>5590</v>
       </c>
-      <c r="D37" s="0" t="n">
+      <c r="D37" s="1" t="n">
         <v>1006</v>
       </c>
     </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="0" t="n">
+        <v>14462</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>8624</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="0" t="n">
+        <v>16642</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>10060</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>1477</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="0" t="n">
+        <v>18966</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>10913</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>397</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="0" t="n">
+        <v>1268</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>8414</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>2602</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>56398</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>4320</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
